--- a/results/Int Task Remove ACC -0.5/Rando_7_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_7_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.712705260680049</v>
+        <v>0.6914985754523243</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7111066016217927</v>
+        <v>0.6988116593748225</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7096838802892927</v>
+        <v>0.698095326996599</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7101169265485361</v>
+        <v>0.7024943789215647</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7107583788566281</v>
+        <v>0.7004951419271573</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7073851230143591</v>
+        <v>0.6998536896190655</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7073851230143591</v>
+        <v>0.7056429945534388</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7088177877708062</v>
+        <v>0.709449296654951</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7019702184306436</v>
+        <v>0.7119564599787332</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7067499614438664</v>
+        <v>0.7049167187512683</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7063917952547546</v>
+        <v>0.6977759198681786</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7068410756755441</v>
+        <v>0.6929050626232782</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7058676347638335</v>
+        <v>0.6864093687346283</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7055806959585055</v>
+        <v>0.6911728775863049</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7023634909940989</v>
+        <v>0.6935726925168633</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.705779158583407</v>
+        <v>0.6899062071316672</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.6926631736162406</v>
+        <v>0.6837912043312744</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.6926631736162406</v>
+        <v>0.6825245338766366</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7041569599909089</v>
+        <v>0.6834655064652548</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7040009091130466</v>
+        <v>0.6963495458493307</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6731992256304942</v>
+        <v>0.689583147316899</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6329437810985657</v>
+        <v>0.6891501010576556</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.639625356136919</v>
+        <v>0.697280575014002</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.6304104401892903</v>
+        <v>0.6964731284041008</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.6271770010633376</v>
+        <v>0.7016110376064353</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.6259689765172853</v>
+        <v>0.6961374871141344</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.6227878925623189</v>
+        <v>0.6889804540694984</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.6227878925623189</v>
+        <v>0.6783302353141716</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6259626857796862</v>
+        <v>0.6687472097534843</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6118894940623554</v>
+        <v>0.6645340389782219</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6011434937539063</v>
+        <v>0.6645340389782219</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.599909291622361</v>
+        <v>0.654244624463258</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5975744133379871</v>
+        <v>0.654244624463258</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.626895338360512</v>
+        <v>0.6583829151683889</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6342120749693581</v>
+        <v>0.6408940558617499</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6406763151700123</v>
+        <v>0.6479437405131618</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6377523397485328</v>
+        <v>0.6327725106942539</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5861110660162179</v>
+        <v>0.6263344480790929</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.5861110660162179</v>
+        <v>0.6330746690260314</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.5908719368166433</v>
+        <v>0.6370893771763924</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5881815303944089</v>
+        <v>0.6386456244876093</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5829713791731941</v>
+        <v>0.6556626784743136</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5822126350479314</v>
+        <v>0.6451585671729019</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5822126350479314</v>
+        <v>0.6457513169963554</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5450236207050496</v>
+        <v>0.6427561141910922</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5453655527326152</v>
+        <v>0.6076093573707152</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.547566905038272</v>
+        <v>0.6190455124718945</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5308556620696933</v>
+        <v>0.5942598034043036</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.5333303570703832</v>
+        <v>0.5929931329496659</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.5338707517228504</v>
+        <v>0.5578908171465213</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.5393280680536052</v>
+        <v>0.5579070513080675</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.533170653506173</v>
+        <v>0.5401422112551442</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5389149086422559</v>
+        <v>0.5398589251361641</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5289511919933115</v>
+        <v>0.5352064173640592</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5360071673823226</v>
+        <v>0.5155072769629131</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5360071673823226</v>
+        <v>0.5179730431747527</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5271703044716998</v>
+        <v>0.4946995462551848</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5181439077250258</v>
+        <v>0.4874136545532765</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5069946914291744</v>
+        <v>0.4833890029789686</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5067862853803259</v>
+        <v>0.4530376145523024</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5024197017784524</v>
+        <v>0.4569774426325316</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5051452145750303</v>
+        <v>0.4445536417282888</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.50486192845605</v>
+        <v>0.4445536417282888</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5030773882480905</v>
+        <v>0.4439870694903285</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.4955035431057574</v>
+        <v>0.4443038385674976</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.497144613911053</v>
+        <v>0.4482211417485815</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.497144613911053</v>
+        <v>0.4485793079376933</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.4964382249567765</v>
+        <v>0.4297137917319415</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.492983798306777</v>
+        <v>0.4306060618359213</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.4862535207837853</v>
+        <v>0.4388412461342403</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4909646744644756</v>
+        <v>0.4173806992053378</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4915050691169428</v>
+        <v>0.4177388653944495</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4990427932498356</v>
+        <v>0.4560924779012476</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4879008823266801</v>
+        <v>0.4536052014253594</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4909809086260217</v>
+        <v>0.4529637491172674</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4907138566685877</v>
+        <v>0.4287283781260908</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4929214997118437</v>
+        <v>0.4401562132194777</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.492188933172074</v>
+        <v>0.4336452998043784</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4933807235565801</v>
+        <v>0.4336452998043784</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4958454751333231</v>
+        <v>0.4418741933650982</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4974540776155264</v>
+        <v>0.4384836887261865</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4993360227927628</v>
+        <v>0.5000038556133672</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4982274324861807</v>
+        <v>0.4879842853316233</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4982274324861807</v>
+        <v>0.4894206027744182</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5023494890297653</v>
+        <v>0.4875548917587279</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5071653530524283</v>
+        <v>0.4880737761471464</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4947322175052964</v>
+        <v>0.495175410115506</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4973828502317427</v>
+        <v>0.495175410115506</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4973828502317427</v>
+        <v>0.5003981428119191</v>
       </c>
     </row>
   </sheetData>
